--- a/Result/profitability/9962.xlsx
+++ b/Result/profitability/9962.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,7 +672,7 @@
         <v>-0.01875000000000006</v>
       </c>
       <c r="N2" t="n">
-        <v>4.46125</v>
+        <v>4.3725</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.29</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.00500000000000006</v>
+        <v>0.00249999999999994</v>
       </c>
       <c r="N3" t="n">
-        <v>3.828749999999999</v>
+        <v>4.115</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>-0.58</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.09250000000000005</v>
+        <v>-0.08500000000000005</v>
       </c>
       <c r="N4" t="n">
-        <v>2.93</v>
+        <v>3.0925</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-4.91</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.7212500000000001</v>
+        <v>-0.6637500000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>-6.41375</v>
+        <v>-5.59125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.11</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7000000000000001</v>
+        <v>-0.6687500000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>-6.765000000000001</v>
+        <v>-6.228750000000001</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.38</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.64375</v>
+        <v>-0.6312500000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>-6.112500000000001</v>
+        <v>-5.987500000000001</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.35</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.61</v>
+        <v>-0.59375</v>
       </c>
       <c r="N8" t="n">
-        <v>-6.1275</v>
+        <v>-6.162500000000001</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1648,7 +1648,7 @@
         <v>-0.48625</v>
       </c>
       <c r="N10" t="n">
-        <v>-5.627500000000001</v>
+        <v>-5.6275</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1775,7 +1775,7 @@
         <v>-0.4237500000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>-5.026250000000001</v>
+        <v>-5.02625</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>9962</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>562</v>
+      </c>
+      <c r="D75" t="n">
+        <v>521</v>
+      </c>
+      <c r="E75" t="n">
+        <v>41</v>
+      </c>
+      <c r="F75" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="G75" t="n">
+        <v>19</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>3.45%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>20</v>
+      </c>
+      <c r="K75" t="n">
+        <v>16</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.04749999999999994</v>
+      </c>
+      <c r="N75" t="n">
+        <v>5.54125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="X75" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.2800000000000002</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.03669724770642202</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.642857142857143</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>8.545454545454545</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
